--- a/docs/relatorios/unidade-SC.xlsx
+++ b/docs/relatorios/unidade-SC.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Não instituída</t>
+          <t>Instituída</t>
         </is>
       </c>
     </row>
@@ -454,6 +454,9 @@
           <t>base_score</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +464,9 @@
           <t>bonus_available</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -468,6 +474,9 @@
           <t>bonus_applied</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -475,6 +484,9 @@
           <t>final_score</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>82.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -494,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Não instituída</t>
+          <t>Instituída — abaixo do mínimo em dimensão essencial</t>
         </is>
       </c>
     </row>
@@ -696,11 +708,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -741,11 +753,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -786,11 +798,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -966,11 +978,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1011,11 +1023,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1056,11 +1068,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1101,11 +1113,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1146,11 +1158,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Não atende</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1191,11 +1203,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1236,11 +1248,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1281,11 +1293,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1326,11 +1338,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1371,11 +1383,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1596,11 +1608,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Não atende</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1686,11 +1698,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sem evidência</t>
+          <t>Atende</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1821,11 +1833,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1866,11 +1878,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1956,11 +1968,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2001,11 +2013,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>

--- a/docs/relatorios/unidade-SC.xlsx
+++ b/docs/relatorios/unidade-SC.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Doc. SEI 37070578</t>
+          <t>Decreto</t>
         </is>
       </c>
     </row>
